--- a/output/yearly_population_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_78_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6689</v>
+        <v>5793</v>
       </c>
       <c r="C2" t="n">
-        <v>7492</v>
+        <v>10045</v>
       </c>
       <c r="D2" t="n">
-        <v>23672</v>
+        <v>41554</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4067</v>
+        <v>3780</v>
       </c>
       <c r="C3" t="n">
-        <v>5193</v>
+        <v>4881</v>
       </c>
       <c r="D3" t="n">
-        <v>13396</v>
+        <v>17661</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3146</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>5329</v>
+        <v>5541</v>
       </c>
       <c r="D4" t="n">
-        <v>6499</v>
+        <v>8989</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2094</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>4424</v>
+        <v>5028</v>
       </c>
       <c r="D5" t="n">
-        <v>2547</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>1043</v>
       </c>
       <c r="C6" t="n">
-        <v>3037</v>
+        <v>3752</v>
       </c>
       <c r="D6" t="n">
-        <v>1082</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>602</v>
+        <v>516</v>
       </c>
       <c r="C7" t="n">
-        <v>1811</v>
+        <v>2377</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C8" t="n">
-        <v>894</v>
+        <v>1066</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7989</v>
+        <v>5803</v>
       </c>
       <c r="C2" t="n">
-        <v>5749</v>
+        <v>14541</v>
       </c>
       <c r="D2" t="n">
-        <v>29005</v>
+        <v>43555</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4291</v>
+        <v>3771</v>
       </c>
       <c r="C3" t="n">
-        <v>5489</v>
+        <v>6260</v>
       </c>
       <c r="D3" t="n">
-        <v>13893</v>
+        <v>19560</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3028</v>
+        <v>2767</v>
       </c>
       <c r="C4" t="n">
-        <v>5152</v>
+        <v>5127</v>
       </c>
       <c r="D4" t="n">
-        <v>7427</v>
+        <v>10047</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2252</v>
+        <v>1960</v>
       </c>
       <c r="C5" t="n">
-        <v>4706</v>
+        <v>5096</v>
       </c>
       <c r="D5" t="n">
-        <v>3052</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1453</v>
+        <v>1233</v>
       </c>
       <c r="C6" t="n">
-        <v>3633</v>
+        <v>4219</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>784</v>
+        <v>651</v>
       </c>
       <c r="C7" t="n">
-        <v>2333</v>
+        <v>2955</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="C8" t="n">
-        <v>1289</v>
+        <v>1581</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>594</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9661</v>
+        <v>7012</v>
       </c>
       <c r="C2" t="n">
-        <v>14026</v>
+        <v>13516</v>
       </c>
       <c r="D2" t="n">
-        <v>22336</v>
+        <v>38951</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4695</v>
+        <v>3713</v>
       </c>
       <c r="C3" t="n">
-        <v>4967</v>
+        <v>8371</v>
       </c>
       <c r="D3" t="n">
-        <v>14817</v>
+        <v>21026</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3014</v>
+        <v>2680</v>
       </c>
       <c r="C4" t="n">
-        <v>5140</v>
+        <v>5427</v>
       </c>
       <c r="D4" t="n">
-        <v>8061</v>
+        <v>10923</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2307</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="n">
-        <v>4751</v>
+        <v>4953</v>
       </c>
       <c r="D5" t="n">
-        <v>3559</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1614</v>
+        <v>1372</v>
       </c>
       <c r="C6" t="n">
-        <v>4043</v>
+        <v>4478</v>
       </c>
       <c r="D6" t="n">
-        <v>1528</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>941</v>
+        <v>779</v>
       </c>
       <c r="C7" t="n">
-        <v>2831</v>
+        <v>3436</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>447</v>
+        <v>368</v>
       </c>
       <c r="C8" t="n">
-        <v>1685</v>
+        <v>2063</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="C9" t="n">
-        <v>859</v>
+        <v>980</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8739</v>
+        <v>6503</v>
       </c>
       <c r="C2" t="n">
-        <v>9537</v>
+        <v>9515</v>
       </c>
       <c r="D2" t="n">
-        <v>18437</v>
+        <v>32371</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5568</v>
+        <v>4561</v>
       </c>
       <c r="C3" t="n">
-        <v>8523</v>
+        <v>11730</v>
       </c>
       <c r="D3" t="n">
-        <v>16131</v>
+        <v>22434</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>1860</v>
       </c>
       <c r="C4" t="n">
-        <v>7422</v>
+        <v>7568</v>
       </c>
       <c r="D4" t="n">
-        <v>7722</v>
+        <v>10331</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1491</v>
+        <v>1267</v>
       </c>
       <c r="C5" t="n">
-        <v>3962</v>
+        <v>4388</v>
       </c>
       <c r="D5" t="n">
-        <v>2454</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>719</v>
       </c>
       <c r="C6" t="n">
-        <v>2774</v>
+        <v>3367</v>
       </c>
       <c r="D6" t="n">
-        <v>741</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>1651</v>
+        <v>2021</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>841</v>
+        <v>960</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5268</v>
+        <v>4131</v>
       </c>
       <c r="C2" t="n">
-        <v>4582</v>
+        <v>4827</v>
       </c>
       <c r="D2" t="n">
-        <v>13154</v>
+        <v>22467</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5927</v>
+        <v>4619</v>
       </c>
       <c r="C3" t="n">
-        <v>8140</v>
+        <v>9810</v>
       </c>
       <c r="D3" t="n">
-        <v>15515</v>
+        <v>22449</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2974</v>
+        <v>2463</v>
       </c>
       <c r="C4" t="n">
-        <v>8070</v>
+        <v>9539</v>
       </c>
       <c r="D4" t="n">
-        <v>8927</v>
+        <v>11958</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1638</v>
+        <v>1406</v>
       </c>
       <c r="C5" t="n">
-        <v>5498</v>
+        <v>5686</v>
       </c>
       <c r="D5" t="n">
-        <v>3083</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>3326</v>
+        <v>3906</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>387</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>2104</v>
+        <v>2508</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1092</v>
+        <v>1267</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6092</v>
+        <v>4587</v>
       </c>
       <c r="C2" t="n">
-        <v>5938</v>
+        <v>6670</v>
       </c>
       <c r="D2" t="n">
-        <v>19699</v>
+        <v>26057</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4741</v>
+        <v>3722</v>
       </c>
       <c r="C3" t="n">
-        <v>5735</v>
+        <v>6695</v>
       </c>
       <c r="D3" t="n">
-        <v>14256</v>
+        <v>21158</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3666</v>
+        <v>2856</v>
       </c>
       <c r="C4" t="n">
-        <v>7936</v>
+        <v>9559</v>
       </c>
       <c r="D4" t="n">
-        <v>9730</v>
+        <v>13205</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1956</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="n">
-        <v>6593</v>
+        <v>7269</v>
       </c>
       <c r="D5" t="n">
-        <v>3886</v>
+        <v>4877</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1186</v>
+        <v>980</v>
       </c>
       <c r="C6" t="n">
-        <v>4306</v>
+        <v>4621</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>570</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>2630</v>
+        <v>3106</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1518</v>
+        <v>1753</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3617</v>
+        <v>2812</v>
       </c>
       <c r="C2" t="n">
-        <v>2819</v>
+        <v>3277</v>
       </c>
       <c r="D2" t="n">
-        <v>13728</v>
+        <v>18382</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4887</v>
+        <v>3776</v>
       </c>
       <c r="C3" t="n">
-        <v>5628</v>
+        <v>6515</v>
       </c>
       <c r="D3" t="n">
-        <v>14502</v>
+        <v>21188</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4050</v>
+        <v>3114</v>
       </c>
       <c r="C4" t="n">
-        <v>7814</v>
+        <v>9425</v>
       </c>
       <c r="D4" t="n">
-        <v>10329</v>
+        <v>14141</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2059</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="n">
-        <v>7836</v>
+        <v>8874</v>
       </c>
       <c r="D5" t="n">
-        <v>4104</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>790</v>
       </c>
       <c r="C6" t="n">
-        <v>5213</v>
+        <v>5440</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2779</v>
+        <v>3198</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1145</v>
+        <v>1208</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4029</v>
+        <v>3293</v>
       </c>
       <c r="C2" t="n">
-        <v>7033</v>
+        <v>7099</v>
       </c>
       <c r="D2" t="n">
-        <v>14334</v>
+        <v>21182</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3726</v>
+        <v>2904</v>
       </c>
       <c r="C3" t="n">
-        <v>3883</v>
+        <v>4573</v>
       </c>
       <c r="D3" t="n">
-        <v>13422</v>
+        <v>19438</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3832</v>
+        <v>2941</v>
       </c>
       <c r="C4" t="n">
-        <v>6623</v>
+        <v>8006</v>
       </c>
       <c r="D4" t="n">
-        <v>10795</v>
+        <v>14793</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2535</v>
+        <v>2002</v>
       </c>
       <c r="C5" t="n">
-        <v>7738</v>
+        <v>9007</v>
       </c>
       <c r="D5" t="n">
-        <v>4875</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1288</v>
+        <v>1019</v>
       </c>
       <c r="C6" t="n">
-        <v>6324</v>
+        <v>6798</v>
       </c>
       <c r="D6" t="n">
-        <v>1573</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>3810</v>
+        <v>4062</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1759</v>
+        <v>1925</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2954</v>
+        <v>2173</v>
       </c>
       <c r="C2" t="n">
-        <v>3655</v>
+        <v>4114</v>
       </c>
       <c r="D2" t="n">
-        <v>10063</v>
+        <v>15188</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>2650</v>
       </c>
       <c r="C3" t="n">
-        <v>4693</v>
+        <v>5063</v>
       </c>
       <c r="D3" t="n">
-        <v>12801</v>
+        <v>18607</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3466</v>
+        <v>2697</v>
       </c>
       <c r="C4" t="n">
-        <v>5507</v>
+        <v>6707</v>
       </c>
       <c r="D4" t="n">
-        <v>10923</v>
+        <v>15065</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2788</v>
+        <v>2147</v>
       </c>
       <c r="C5" t="n">
-        <v>7467</v>
+        <v>8829</v>
       </c>
       <c r="D5" t="n">
-        <v>5502</v>
+        <v>7053</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1510</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>7025</v>
+        <v>7703</v>
       </c>
       <c r="D6" t="n">
-        <v>1870</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>4685</v>
+        <v>4928</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2263</v>
+        <v>2404</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>597</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4643</v>
+        <v>3882</v>
       </c>
       <c r="C2" t="n">
-        <v>10651</v>
+        <v>10352</v>
       </c>
       <c r="D2" t="n">
-        <v>11275</v>
+        <v>18186</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2701</v>
+        <v>2103</v>
       </c>
       <c r="C3" t="n">
-        <v>3838</v>
+        <v>4249</v>
       </c>
       <c r="D3" t="n">
-        <v>11653</v>
+        <v>17062</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2976</v>
+        <v>2330</v>
       </c>
       <c r="C4" t="n">
-        <v>5048</v>
+        <v>5920</v>
       </c>
       <c r="D4" t="n">
-        <v>10861</v>
+        <v>15083</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2781</v>
+        <v>2120</v>
       </c>
       <c r="C5" t="n">
-        <v>6521</v>
+        <v>7766</v>
       </c>
       <c r="D5" t="n">
-        <v>6063</v>
+        <v>7838</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1803</v>
+        <v>1375</v>
       </c>
       <c r="C6" t="n">
-        <v>7135</v>
+        <v>8127</v>
       </c>
       <c r="D6" t="n">
-        <v>2281</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>637</v>
+        <v>465</v>
       </c>
       <c r="C7" t="n">
-        <v>5554</v>
+        <v>5877</v>
       </c>
       <c r="D7" t="n">
-        <v>869</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>3138</v>
+        <v>3219</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1194</v>
+        <v>1151</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7732</v>
+        <v>7308</v>
       </c>
       <c r="C2" t="n">
-        <v>7799</v>
+        <v>8825</v>
       </c>
       <c r="D2" t="n">
-        <v>6486</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3323</v>
+        <v>2866</v>
       </c>
       <c r="C2" t="n">
-        <v>6049</v>
+        <v>6128</v>
       </c>
       <c r="D2" t="n">
-        <v>8299</v>
+        <v>13530</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>2834</v>
       </c>
       <c r="C3" t="n">
-        <v>5750</v>
+        <v>6019</v>
       </c>
       <c r="D3" t="n">
-        <v>12638</v>
+        <v>18556</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4064</v>
+        <v>3149</v>
       </c>
       <c r="C4" t="n">
-        <v>7254</v>
+        <v>8505</v>
       </c>
       <c r="D4" t="n">
-        <v>11151</v>
+        <v>15277</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1743</v>
+        <v>1270</v>
       </c>
       <c r="C5" t="n">
-        <v>9850</v>
+        <v>11456</v>
       </c>
       <c r="D5" t="n">
-        <v>5483</v>
+        <v>6903</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>588</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>6841</v>
+        <v>7113</v>
       </c>
       <c r="D6" t="n">
-        <v>1858</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3075</v>
+        <v>3154</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1170</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8374</v>
+        <v>7670</v>
       </c>
       <c r="C2" t="n">
-        <v>6394</v>
+        <v>10492</v>
       </c>
       <c r="D2" t="n">
-        <v>8592</v>
+        <v>23828</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3283</v>
+        <v>3104</v>
       </c>
       <c r="C3" t="n">
-        <v>3930</v>
+        <v>4447</v>
       </c>
       <c r="D3" t="n">
-        <v>1728</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5897</v>
+        <v>5399</v>
       </c>
       <c r="C2" t="n">
-        <v>3871</v>
+        <v>9454</v>
       </c>
       <c r="D2" t="n">
-        <v>25635</v>
+        <v>30015</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4787</v>
+        <v>4425</v>
       </c>
       <c r="C3" t="n">
-        <v>4591</v>
+        <v>6785</v>
       </c>
       <c r="D3" t="n">
-        <v>2753</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1460</v>
+        <v>1383</v>
       </c>
       <c r="C4" t="n">
-        <v>2346</v>
+        <v>2650</v>
       </c>
       <c r="D4" t="n">
-        <v>1529</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5299</v>
+        <v>4676</v>
       </c>
       <c r="C2" t="n">
-        <v>9316</v>
+        <v>5712</v>
       </c>
       <c r="D2" t="n">
-        <v>27458</v>
+        <v>34265</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4391</v>
+        <v>4033</v>
       </c>
       <c r="C3" t="n">
-        <v>3634</v>
+        <v>7122</v>
       </c>
       <c r="D3" t="n">
-        <v>6215</v>
+        <v>9532</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2657</v>
+        <v>2434</v>
       </c>
       <c r="C4" t="n">
-        <v>3568</v>
+        <v>4897</v>
       </c>
       <c r="D4" t="n">
-        <v>1717</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>1379</v>
+        <v>1524</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6165</v>
+        <v>4599</v>
       </c>
       <c r="C2" t="n">
-        <v>6005</v>
+        <v>7364</v>
       </c>
       <c r="D2" t="n">
-        <v>24453</v>
+        <v>31367</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4012</v>
+        <v>3610</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>5589</v>
       </c>
       <c r="D3" t="n">
-        <v>9006</v>
+        <v>12711</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2965</v>
+        <v>2707</v>
       </c>
       <c r="C4" t="n">
-        <v>3529</v>
+        <v>5969</v>
       </c>
       <c r="D4" t="n">
-        <v>2485</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>1237</v>
       </c>
       <c r="C5" t="n">
-        <v>2485</v>
+        <v>3208</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C6" t="n">
-        <v>834</v>
+        <v>895</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
         <v>664</v>
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7384</v>
+        <v>7008</v>
       </c>
       <c r="C2" t="n">
-        <v>8692</v>
+        <v>10521</v>
       </c>
       <c r="D2" t="n">
-        <v>22273</v>
+        <v>34229</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3676</v>
+        <v>2970</v>
       </c>
       <c r="C3" t="n">
-        <v>4800</v>
+        <v>5300</v>
       </c>
       <c r="D3" t="n">
-        <v>10085</v>
+        <v>13649</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2153</v>
+        <v>1954</v>
       </c>
       <c r="C4" t="n">
-        <v>3874</v>
+        <v>4666</v>
       </c>
       <c r="D4" t="n">
-        <v>3142</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1134</v>
+        <v>1012</v>
       </c>
       <c r="C5" t="n">
-        <v>2190</v>
+        <v>3367</v>
       </c>
       <c r="D5" t="n">
-        <v>1139</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="C6" t="n">
-        <v>1122</v>
+        <v>1356</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6070</v>
+        <v>6434</v>
       </c>
       <c r="C2" t="n">
-        <v>7040</v>
+        <v>5276</v>
       </c>
       <c r="D2" t="n">
-        <v>20391</v>
+        <v>25856</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4602</v>
+        <v>4099</v>
       </c>
       <c r="C3" t="n">
-        <v>6085</v>
+        <v>7118</v>
       </c>
       <c r="D3" t="n">
-        <v>11390</v>
+        <v>16101</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2558</v>
+        <v>2139</v>
       </c>
       <c r="C4" t="n">
-        <v>4353</v>
+        <v>4940</v>
       </c>
       <c r="D4" t="n">
-        <v>4416</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>1302</v>
       </c>
       <c r="C5" t="n">
-        <v>3130</v>
+        <v>4032</v>
       </c>
       <c r="D5" t="n">
-        <v>1508</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>628</v>
       </c>
       <c r="C6" t="n">
-        <v>1702</v>
+        <v>2427</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>799</v>
+        <v>918</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5598</v>
+        <v>4961</v>
       </c>
       <c r="C2" t="n">
-        <v>6179</v>
+        <v>5786</v>
       </c>
       <c r="D2" t="n">
-        <v>27376</v>
+        <v>32726</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4379</v>
+        <v>4270</v>
       </c>
       <c r="C3" t="n">
-        <v>5717</v>
+        <v>5370</v>
       </c>
       <c r="D3" t="n">
-        <v>12010</v>
+        <v>16450</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3076</v>
+        <v>2625</v>
       </c>
       <c r="C4" t="n">
-        <v>5243</v>
+        <v>5960</v>
       </c>
       <c r="D4" t="n">
-        <v>5620</v>
+        <v>7715</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1757</v>
+        <v>1512</v>
       </c>
       <c r="C5" t="n">
-        <v>3734</v>
+        <v>4427</v>
       </c>
       <c r="D5" t="n">
-        <v>1978</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>860</v>
       </c>
       <c r="C6" t="n">
-        <v>2419</v>
+        <v>3216</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>1276</v>
+        <v>1662</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>557</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_78_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5793</v>
+        <v>8709</v>
       </c>
       <c r="C2" t="n">
-        <v>10045</v>
+        <v>4709</v>
       </c>
       <c r="D2" t="n">
-        <v>41554</v>
+        <v>26260</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3780</v>
+        <v>5543</v>
       </c>
       <c r="C3" t="n">
-        <v>4881</v>
+        <v>5548</v>
       </c>
       <c r="D3" t="n">
-        <v>17661</v>
+        <v>14397</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>3905</v>
       </c>
       <c r="C4" t="n">
-        <v>5541</v>
+        <v>2956</v>
       </c>
       <c r="D4" t="n">
-        <v>8989</v>
+        <v>6752</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>2481</v>
       </c>
       <c r="C5" t="n">
-        <v>5028</v>
+        <v>2518</v>
       </c>
       <c r="D5" t="n">
-        <v>3412</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1043</v>
+        <v>1370</v>
       </c>
       <c r="C6" t="n">
-        <v>3752</v>
+        <v>1970</v>
       </c>
       <c r="D6" t="n">
-        <v>1272</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>516</v>
+        <v>652</v>
       </c>
       <c r="C7" t="n">
-        <v>2377</v>
+        <v>1286</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="C8" t="n">
-        <v>1066</v>
+        <v>658</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>406</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5803</v>
+        <v>10459</v>
       </c>
       <c r="C2" t="n">
-        <v>14541</v>
+        <v>6335</v>
       </c>
       <c r="D2" t="n">
-        <v>43555</v>
+        <v>26877</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3771</v>
+        <v>5687</v>
       </c>
       <c r="C3" t="n">
-        <v>6260</v>
+        <v>4515</v>
       </c>
       <c r="D3" t="n">
-        <v>19560</v>
+        <v>15114</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2767</v>
+        <v>3960</v>
       </c>
       <c r="C4" t="n">
-        <v>5127</v>
+        <v>4188</v>
       </c>
       <c r="D4" t="n">
-        <v>10047</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1960</v>
+        <v>2749</v>
       </c>
       <c r="C5" t="n">
-        <v>5096</v>
+        <v>2651</v>
       </c>
       <c r="D5" t="n">
-        <v>4078</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>1712</v>
       </c>
       <c r="C6" t="n">
-        <v>4219</v>
+        <v>2207</v>
       </c>
       <c r="D6" t="n">
-        <v>1563</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>651</v>
+        <v>867</v>
       </c>
       <c r="C7" t="n">
-        <v>2955</v>
+        <v>1587</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="C8" t="n">
-        <v>1581</v>
+        <v>940</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7012</v>
+        <v>12408</v>
       </c>
       <c r="C2" t="n">
-        <v>13516</v>
+        <v>5261</v>
       </c>
       <c r="D2" t="n">
-        <v>38951</v>
+        <v>33136</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3713</v>
+        <v>6254</v>
       </c>
       <c r="C3" t="n">
-        <v>8371</v>
+        <v>4686</v>
       </c>
       <c r="D3" t="n">
-        <v>21026</v>
+        <v>15628</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2680</v>
+        <v>3996</v>
       </c>
       <c r="C4" t="n">
-        <v>5427</v>
+        <v>4251</v>
       </c>
       <c r="D4" t="n">
-        <v>10923</v>
+        <v>8665</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>2916</v>
       </c>
       <c r="C5" t="n">
-        <v>4953</v>
+        <v>3249</v>
       </c>
       <c r="D5" t="n">
-        <v>4717</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1372</v>
+        <v>1952</v>
       </c>
       <c r="C6" t="n">
-        <v>4478</v>
+        <v>2356</v>
       </c>
       <c r="D6" t="n">
-        <v>1880</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>779</v>
+        <v>1090</v>
       </c>
       <c r="C7" t="n">
-        <v>3436</v>
+        <v>1853</v>
       </c>
       <c r="D7" t="n">
-        <v>824</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>368</v>
+        <v>512</v>
       </c>
       <c r="C8" t="n">
-        <v>2063</v>
+        <v>1196</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="C9" t="n">
-        <v>980</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6503</v>
+        <v>11168</v>
       </c>
       <c r="C2" t="n">
-        <v>9515</v>
+        <v>3493</v>
       </c>
       <c r="D2" t="n">
-        <v>32371</v>
+        <v>26843</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4561</v>
+        <v>7507</v>
       </c>
       <c r="C3" t="n">
-        <v>11730</v>
+        <v>6846</v>
       </c>
       <c r="D3" t="n">
-        <v>22434</v>
+        <v>17246</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1860</v>
+        <v>2694</v>
       </c>
       <c r="C4" t="n">
-        <v>7568</v>
+        <v>5567</v>
       </c>
       <c r="D4" t="n">
-        <v>10331</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1267</v>
+        <v>1803</v>
       </c>
       <c r="C5" t="n">
-        <v>4388</v>
+        <v>2308</v>
       </c>
       <c r="D5" t="n">
-        <v>3065</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>1007</v>
       </c>
       <c r="C6" t="n">
-        <v>3367</v>
+        <v>1815</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>473</v>
       </c>
       <c r="C7" t="n">
-        <v>2021</v>
+        <v>1172</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="C8" t="n">
-        <v>960</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4131</v>
+        <v>6782</v>
       </c>
       <c r="C2" t="n">
-        <v>4827</v>
+        <v>2055</v>
       </c>
       <c r="D2" t="n">
-        <v>22467</v>
+        <v>18661</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4619</v>
+        <v>7845</v>
       </c>
       <c r="C3" t="n">
-        <v>9810</v>
+        <v>4795</v>
       </c>
       <c r="D3" t="n">
-        <v>22449</v>
+        <v>17772</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2463</v>
+        <v>3978</v>
       </c>
       <c r="C4" t="n">
-        <v>9539</v>
+        <v>6225</v>
       </c>
       <c r="D4" t="n">
-        <v>11958</v>
+        <v>9489</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1406</v>
+        <v>2035</v>
       </c>
       <c r="C5" t="n">
-        <v>5686</v>
+        <v>3778</v>
       </c>
       <c r="D5" t="n">
-        <v>3867</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>1224</v>
       </c>
       <c r="C6" t="n">
-        <v>3906</v>
+        <v>2104</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>448</v>
       </c>
       <c r="C7" t="n">
-        <v>2508</v>
+        <v>1446</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>1267</v>
+        <v>834</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>424</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4587</v>
+        <v>7591</v>
       </c>
       <c r="C2" t="n">
-        <v>6670</v>
+        <v>5167</v>
       </c>
       <c r="D2" t="n">
-        <v>26057</v>
+        <v>18415</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3722</v>
+        <v>6184</v>
       </c>
       <c r="C3" t="n">
-        <v>6695</v>
+        <v>3005</v>
       </c>
       <c r="D3" t="n">
-        <v>21158</v>
+        <v>16677</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2856</v>
+        <v>4940</v>
       </c>
       <c r="C4" t="n">
-        <v>9559</v>
+        <v>5413</v>
       </c>
       <c r="D4" t="n">
-        <v>13205</v>
+        <v>10631</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>2555</v>
       </c>
       <c r="C5" t="n">
-        <v>7269</v>
+        <v>4897</v>
       </c>
       <c r="D5" t="n">
-        <v>4877</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>980</v>
+        <v>1460</v>
       </c>
       <c r="C6" t="n">
-        <v>4621</v>
+        <v>2890</v>
       </c>
       <c r="D6" t="n">
-        <v>1413</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>670</v>
       </c>
       <c r="C7" t="n">
-        <v>3106</v>
+        <v>1756</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="C8" t="n">
-        <v>1753</v>
+        <v>1099</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>725</v>
+        <v>565</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2812</v>
+        <v>4449</v>
       </c>
       <c r="C2" t="n">
-        <v>3277</v>
+        <v>2284</v>
       </c>
       <c r="D2" t="n">
-        <v>18382</v>
+        <v>12695</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3776</v>
+        <v>6308</v>
       </c>
       <c r="C3" t="n">
-        <v>6515</v>
+        <v>3677</v>
       </c>
       <c r="D3" t="n">
-        <v>21188</v>
+        <v>16471</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3114</v>
+        <v>5476</v>
       </c>
       <c r="C4" t="n">
-        <v>9425</v>
+        <v>4964</v>
       </c>
       <c r="D4" t="n">
-        <v>14141</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>2664</v>
       </c>
       <c r="C5" t="n">
-        <v>8874</v>
+        <v>5709</v>
       </c>
       <c r="D5" t="n">
-        <v>5007</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>790</v>
+        <v>1239</v>
       </c>
       <c r="C6" t="n">
-        <v>5440</v>
+        <v>3639</v>
       </c>
       <c r="D6" t="n">
-        <v>1367</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>3198</v>
+        <v>1915</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1208</v>
+        <v>919</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3293</v>
+        <v>5514</v>
       </c>
       <c r="C2" t="n">
-        <v>7099</v>
+        <v>3428</v>
       </c>
       <c r="D2" t="n">
-        <v>21182</v>
+        <v>13720</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2904</v>
+        <v>4647</v>
       </c>
       <c r="C3" t="n">
-        <v>4573</v>
+        <v>2662</v>
       </c>
       <c r="D3" t="n">
-        <v>19438</v>
+        <v>14952</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2941</v>
+        <v>5149</v>
       </c>
       <c r="C4" t="n">
-        <v>8006</v>
+        <v>4265</v>
       </c>
       <c r="D4" t="n">
-        <v>14793</v>
+        <v>11879</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2002</v>
+        <v>3397</v>
       </c>
       <c r="C5" t="n">
-        <v>9007</v>
+        <v>5294</v>
       </c>
       <c r="D5" t="n">
-        <v>6218</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1019</v>
+        <v>1649</v>
       </c>
       <c r="C6" t="n">
-        <v>6798</v>
+        <v>4553</v>
       </c>
       <c r="D6" t="n">
-        <v>1803</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>4062</v>
+        <v>2678</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1925</v>
+        <v>1317</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2173</v>
+        <v>4249</v>
       </c>
       <c r="C2" t="n">
-        <v>4114</v>
+        <v>2312</v>
       </c>
       <c r="D2" t="n">
-        <v>15188</v>
+        <v>10410</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2650</v>
+        <v>4328</v>
       </c>
       <c r="C3" t="n">
-        <v>5063</v>
+        <v>2721</v>
       </c>
       <c r="D3" t="n">
-        <v>18607</v>
+        <v>13956</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>4596</v>
       </c>
       <c r="C4" t="n">
-        <v>6707</v>
+        <v>3565</v>
       </c>
       <c r="D4" t="n">
-        <v>15065</v>
+        <v>12074</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2147</v>
+        <v>3764</v>
       </c>
       <c r="C5" t="n">
-        <v>8829</v>
+        <v>4982</v>
       </c>
       <c r="D5" t="n">
-        <v>7053</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>1975</v>
       </c>
       <c r="C6" t="n">
-        <v>7703</v>
+        <v>4991</v>
       </c>
       <c r="D6" t="n">
-        <v>2156</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>488</v>
       </c>
       <c r="C7" t="n">
-        <v>4928</v>
+        <v>3375</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>2404</v>
+        <v>1708</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3882</v>
+        <v>7336</v>
       </c>
       <c r="C2" t="n">
-        <v>10352</v>
+        <v>3775</v>
       </c>
       <c r="D2" t="n">
-        <v>18186</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2103</v>
+        <v>3611</v>
       </c>
       <c r="C3" t="n">
-        <v>4249</v>
+        <v>2272</v>
       </c>
       <c r="D3" t="n">
-        <v>17062</v>
+        <v>12586</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2330</v>
+        <v>3907</v>
       </c>
       <c r="C4" t="n">
-        <v>5920</v>
+        <v>3110</v>
       </c>
       <c r="D4" t="n">
-        <v>15083</v>
+        <v>11996</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2120</v>
+        <v>3705</v>
       </c>
       <c r="C5" t="n">
-        <v>7766</v>
+        <v>4266</v>
       </c>
       <c r="D5" t="n">
-        <v>7838</v>
+        <v>6877</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1375</v>
+        <v>2441</v>
       </c>
       <c r="C6" t="n">
-        <v>8127</v>
+        <v>4942</v>
       </c>
       <c r="D6" t="n">
-        <v>2671</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>894</v>
       </c>
       <c r="C7" t="n">
-        <v>5877</v>
+        <v>4022</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>3219</v>
+        <v>2361</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>1151</v>
+        <v>1010</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7308</v>
+        <v>9382</v>
       </c>
       <c r="C2" t="n">
-        <v>8825</v>
+        <v>5415</v>
       </c>
       <c r="D2" t="n">
-        <v>13120</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2866</v>
+        <v>5081</v>
       </c>
       <c r="C2" t="n">
-        <v>6128</v>
+        <v>2053</v>
       </c>
       <c r="D2" t="n">
-        <v>13530</v>
+        <v>9067</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2834</v>
+        <v>5063</v>
       </c>
       <c r="C3" t="n">
-        <v>6019</v>
+        <v>2842</v>
       </c>
       <c r="D3" t="n">
-        <v>18556</v>
+        <v>13670</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3149</v>
+        <v>5415</v>
       </c>
       <c r="C4" t="n">
-        <v>8505</v>
+        <v>4478</v>
       </c>
       <c r="D4" t="n">
-        <v>15277</v>
+        <v>12409</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1270</v>
+        <v>2426</v>
       </c>
       <c r="C5" t="n">
-        <v>11456</v>
+        <v>6636</v>
       </c>
       <c r="D5" t="n">
-        <v>6903</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>429</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>7113</v>
+        <v>5055</v>
       </c>
       <c r="D6" t="n">
-        <v>2067</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>3154</v>
+        <v>2313</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>989</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7670</v>
+        <v>7966</v>
       </c>
       <c r="C2" t="n">
-        <v>10492</v>
+        <v>2983</v>
       </c>
       <c r="D2" t="n">
-        <v>23828</v>
+        <v>13082</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3104</v>
+        <v>3983</v>
       </c>
       <c r="C3" t="n">
-        <v>4447</v>
+        <v>2729</v>
       </c>
       <c r="D3" t="n">
-        <v>2843</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5399</v>
+        <v>5281</v>
       </c>
       <c r="C2" t="n">
-        <v>9454</v>
+        <v>5325</v>
       </c>
       <c r="D2" t="n">
-        <v>30015</v>
+        <v>16379</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4425</v>
+        <v>4912</v>
       </c>
       <c r="C3" t="n">
-        <v>6785</v>
+        <v>2477</v>
       </c>
       <c r="D3" t="n">
-        <v>6159</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1383</v>
+        <v>1764</v>
       </c>
       <c r="C4" t="n">
-        <v>2650</v>
+        <v>1641</v>
       </c>
       <c r="D4" t="n">
-        <v>1754</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4676</v>
+        <v>5675</v>
       </c>
       <c r="C2" t="n">
-        <v>5712</v>
+        <v>3489</v>
       </c>
       <c r="D2" t="n">
-        <v>34265</v>
+        <v>24811</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4033</v>
+        <v>4204</v>
       </c>
       <c r="C3" t="n">
-        <v>7122</v>
+        <v>3488</v>
       </c>
       <c r="D3" t="n">
-        <v>9532</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2434</v>
+        <v>2832</v>
       </c>
       <c r="C4" t="n">
-        <v>4897</v>
+        <v>2080</v>
       </c>
       <c r="D4" t="n">
-        <v>2546</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>617</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>1524</v>
+        <v>990</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4599</v>
+        <v>8729</v>
       </c>
       <c r="C2" t="n">
-        <v>7364</v>
+        <v>3838</v>
       </c>
       <c r="D2" t="n">
-        <v>31367</v>
+        <v>24489</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3610</v>
+        <v>4032</v>
       </c>
       <c r="C3" t="n">
-        <v>5589</v>
+        <v>3036</v>
       </c>
       <c r="D3" t="n">
-        <v>12711</v>
+        <v>7918</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2707</v>
+        <v>2986</v>
       </c>
       <c r="C4" t="n">
-        <v>5969</v>
+        <v>2773</v>
       </c>
       <c r="D4" t="n">
-        <v>3651</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1237</v>
+        <v>1515</v>
       </c>
       <c r="C5" t="n">
-        <v>3208</v>
+        <v>1544</v>
       </c>
       <c r="D5" t="n">
-        <v>1445</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>325</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>895</v>
+        <v>649</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7008</v>
+        <v>9184</v>
       </c>
       <c r="C2" t="n">
-        <v>10521</v>
+        <v>4256</v>
       </c>
       <c r="D2" t="n">
-        <v>34229</v>
+        <v>30764</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>4609</v>
       </c>
       <c r="C3" t="n">
-        <v>5300</v>
+        <v>2827</v>
       </c>
       <c r="D3" t="n">
-        <v>13649</v>
+        <v>9294</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1954</v>
+        <v>2193</v>
       </c>
       <c r="C4" t="n">
-        <v>4666</v>
+        <v>2395</v>
       </c>
       <c r="D4" t="n">
-        <v>4420</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1012</v>
+        <v>1182</v>
       </c>
       <c r="C5" t="n">
-        <v>3367</v>
+        <v>1603</v>
       </c>
       <c r="D5" t="n">
-        <v>1443</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>1356</v>
+        <v>737</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>386</v>
+        <v>319</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>78</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6434</v>
+        <v>7209</v>
       </c>
       <c r="C2" t="n">
-        <v>5276</v>
+        <v>4066</v>
       </c>
       <c r="D2" t="n">
-        <v>25856</v>
+        <v>21591</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4099</v>
+        <v>5773</v>
       </c>
       <c r="C3" t="n">
-        <v>7118</v>
+        <v>3156</v>
       </c>
       <c r="D3" t="n">
-        <v>16101</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2139</v>
+        <v>3017</v>
       </c>
       <c r="C4" t="n">
-        <v>4940</v>
+        <v>2610</v>
       </c>
       <c r="D4" t="n">
-        <v>6146</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1302</v>
+        <v>1517</v>
       </c>
       <c r="C5" t="n">
-        <v>4032</v>
+        <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>1970</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>628</v>
+        <v>760</v>
       </c>
       <c r="C6" t="n">
-        <v>2427</v>
+        <v>1234</v>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>820</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>918</v>
+        <v>560</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4961</v>
+        <v>8328</v>
       </c>
       <c r="C2" t="n">
-        <v>5786</v>
+        <v>9403</v>
       </c>
       <c r="D2" t="n">
-        <v>32726</v>
+        <v>28434</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4270</v>
+        <v>5342</v>
       </c>
       <c r="C3" t="n">
-        <v>5370</v>
+        <v>3163</v>
       </c>
       <c r="D3" t="n">
-        <v>16450</v>
+        <v>12957</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2625</v>
+        <v>3770</v>
       </c>
       <c r="C4" t="n">
-        <v>5960</v>
+        <v>2845</v>
       </c>
       <c r="D4" t="n">
-        <v>7715</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1512</v>
+        <v>2002</v>
       </c>
       <c r="C5" t="n">
-        <v>4427</v>
+        <v>2314</v>
       </c>
       <c r="D5" t="n">
-        <v>2671</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>860</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>3216</v>
+        <v>1652</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>1662</v>
+        <v>923</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>607</v>
+        <v>423</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_78_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8709</v>
+        <v>1600</v>
       </c>
       <c r="C2" t="n">
-        <v>4709</v>
+        <v>5017</v>
       </c>
       <c r="D2" t="n">
-        <v>26260</v>
+        <v>12718</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5543</v>
+        <v>2042</v>
       </c>
       <c r="C3" t="n">
-        <v>5548</v>
+        <v>11253</v>
       </c>
       <c r="D3" t="n">
-        <v>14397</v>
+        <v>12467</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3905</v>
+        <v>1090</v>
       </c>
       <c r="C4" t="n">
-        <v>2956</v>
+        <v>10469</v>
       </c>
       <c r="D4" t="n">
-        <v>6752</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2481</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>2518</v>
+        <v>5357</v>
       </c>
       <c r="D5" t="n">
-        <v>2506</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1370</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>1970</v>
+        <v>2350</v>
       </c>
       <c r="D6" t="n">
-        <v>1089</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>652</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1286</v>
+        <v>876</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>658</v>
+        <v>364</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10459</v>
+        <v>1479</v>
       </c>
       <c r="C2" t="n">
-        <v>6335</v>
+        <v>9357</v>
       </c>
       <c r="D2" t="n">
-        <v>26877</v>
+        <v>20108</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5687</v>
+        <v>1545</v>
       </c>
       <c r="C3" t="n">
-        <v>4515</v>
+        <v>7108</v>
       </c>
       <c r="D3" t="n">
-        <v>15114</v>
+        <v>11627</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3960</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="n">
-        <v>4188</v>
+        <v>10665</v>
       </c>
       <c r="D4" t="n">
-        <v>7867</v>
+        <v>7154</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2749</v>
+        <v>705</v>
       </c>
       <c r="C5" t="n">
-        <v>2651</v>
+        <v>7897</v>
       </c>
       <c r="D5" t="n">
-        <v>3098</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1712</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>2207</v>
+        <v>3791</v>
       </c>
       <c r="D6" t="n">
-        <v>1305</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>867</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>1587</v>
+        <v>1563</v>
       </c>
       <c r="D7" t="n">
-        <v>700</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>940</v>
+        <v>588</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12408</v>
+        <v>808</v>
       </c>
       <c r="C2" t="n">
-        <v>5261</v>
+        <v>4118</v>
       </c>
       <c r="D2" t="n">
-        <v>33136</v>
+        <v>13726</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6254</v>
+        <v>1471</v>
       </c>
       <c r="C3" t="n">
-        <v>4686</v>
+        <v>7674</v>
       </c>
       <c r="D3" t="n">
-        <v>15628</v>
+        <v>12347</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3996</v>
+        <v>1460</v>
       </c>
       <c r="C4" t="n">
-        <v>4251</v>
+        <v>10169</v>
       </c>
       <c r="D4" t="n">
-        <v>8665</v>
+        <v>7752</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2916</v>
+        <v>705</v>
       </c>
       <c r="C5" t="n">
-        <v>3249</v>
+        <v>9635</v>
       </c>
       <c r="D5" t="n">
-        <v>3736</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1952</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>2356</v>
+        <v>4767</v>
       </c>
       <c r="D6" t="n">
-        <v>1533</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1090</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>1853</v>
+        <v>1467</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>512</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11168</v>
+        <v>747</v>
       </c>
       <c r="C2" t="n">
-        <v>3493</v>
+        <v>9541</v>
       </c>
       <c r="D2" t="n">
-        <v>26843</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7507</v>
+        <v>1011</v>
       </c>
       <c r="C3" t="n">
-        <v>6846</v>
+        <v>5282</v>
       </c>
       <c r="D3" t="n">
-        <v>17246</v>
+        <v>11814</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2694</v>
+        <v>1297</v>
       </c>
       <c r="C4" t="n">
-        <v>5567</v>
+        <v>8809</v>
       </c>
       <c r="D4" t="n">
-        <v>8286</v>
+        <v>8266</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1803</v>
+        <v>902</v>
       </c>
       <c r="C5" t="n">
-        <v>2308</v>
+        <v>9778</v>
       </c>
       <c r="D5" t="n">
-        <v>2542</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1007</v>
+        <v>396</v>
       </c>
       <c r="C6" t="n">
-        <v>1815</v>
+        <v>6917</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>1172</v>
+        <v>2885</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>188</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>641</v>
+        <v>882</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6782</v>
+        <v>382</v>
       </c>
       <c r="C2" t="n">
-        <v>2055</v>
+        <v>4624</v>
       </c>
       <c r="D2" t="n">
-        <v>18661</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7845</v>
+        <v>804</v>
       </c>
       <c r="C3" t="n">
-        <v>4795</v>
+        <v>6452</v>
       </c>
       <c r="D3" t="n">
-        <v>17772</v>
+        <v>11069</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3978</v>
+        <v>1113</v>
       </c>
       <c r="C4" t="n">
-        <v>6225</v>
+        <v>7355</v>
       </c>
       <c r="D4" t="n">
-        <v>9489</v>
+        <v>8684</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2035</v>
+        <v>984</v>
       </c>
       <c r="C5" t="n">
-        <v>3778</v>
+        <v>9577</v>
       </c>
       <c r="D5" t="n">
-        <v>3309</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1224</v>
+        <v>490</v>
       </c>
       <c r="C6" t="n">
-        <v>2104</v>
+        <v>8139</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>448</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1446</v>
+        <v>4148</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>834</v>
+        <v>1322</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7591</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>5167</v>
+        <v>13946</v>
       </c>
       <c r="D2" t="n">
-        <v>18415</v>
+        <v>9619</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6184</v>
+        <v>543</v>
       </c>
       <c r="C3" t="n">
-        <v>3005</v>
+        <v>5021</v>
       </c>
       <c r="D3" t="n">
-        <v>16677</v>
+        <v>9978</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4940</v>
+        <v>876</v>
       </c>
       <c r="C4" t="n">
-        <v>5413</v>
+        <v>6794</v>
       </c>
       <c r="D4" t="n">
-        <v>10631</v>
+        <v>8786</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2555</v>
+        <v>941</v>
       </c>
       <c r="C5" t="n">
-        <v>4897</v>
+        <v>8509</v>
       </c>
       <c r="D5" t="n">
-        <v>4216</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1460</v>
+        <v>616</v>
       </c>
       <c r="C6" t="n">
-        <v>2890</v>
+        <v>8647</v>
       </c>
       <c r="D6" t="n">
-        <v>1297</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>670</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
-        <v>1756</v>
+        <v>5710</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1099</v>
+        <v>2386</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>565</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>136</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>278</v>
       </c>
       <c r="C2" t="n">
-        <v>2284</v>
+        <v>7698</v>
       </c>
       <c r="D2" t="n">
-        <v>12695</v>
+        <v>7079</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6308</v>
+        <v>772</v>
       </c>
       <c r="C3" t="n">
-        <v>3677</v>
+        <v>7652</v>
       </c>
       <c r="D3" t="n">
-        <v>16471</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5476</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>4964</v>
+        <v>9681</v>
       </c>
       <c r="D4" t="n">
-        <v>11398</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2664</v>
+        <v>603</v>
       </c>
       <c r="C5" t="n">
-        <v>5709</v>
+        <v>12330</v>
       </c>
       <c r="D5" t="n">
-        <v>4582</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1239</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>3639</v>
+        <v>7375</v>
       </c>
       <c r="D6" t="n">
-        <v>1279</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>1915</v>
+        <v>2338</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>919</v>
+        <v>717</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5514</v>
+        <v>160</v>
       </c>
       <c r="C2" t="n">
-        <v>3428</v>
+        <v>3771</v>
       </c>
       <c r="D2" t="n">
-        <v>13720</v>
+        <v>5705</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4647</v>
+        <v>490</v>
       </c>
       <c r="C3" t="n">
-        <v>2662</v>
+        <v>6789</v>
       </c>
       <c r="D3" t="n">
-        <v>14952</v>
+        <v>9456</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5149</v>
+        <v>896</v>
       </c>
       <c r="C4" t="n">
-        <v>4265</v>
+        <v>8240</v>
       </c>
       <c r="D4" t="n">
-        <v>11879</v>
+        <v>8627</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3397</v>
+        <v>610</v>
       </c>
       <c r="C5" t="n">
-        <v>5294</v>
+        <v>9779</v>
       </c>
       <c r="D5" t="n">
-        <v>5489</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1649</v>
+        <v>198</v>
       </c>
       <c r="C6" t="n">
-        <v>4553</v>
+        <v>7725</v>
       </c>
       <c r="D6" t="n">
-        <v>1737</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>47</v>
       </c>
       <c r="C7" t="n">
-        <v>2678</v>
+        <v>3094</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1317</v>
+        <v>827</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4249</v>
+        <v>363</v>
       </c>
       <c r="C2" t="n">
-        <v>2312</v>
+        <v>6830</v>
       </c>
       <c r="D2" t="n">
-        <v>10410</v>
+        <v>13620</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4328</v>
+        <v>288</v>
       </c>
       <c r="C3" t="n">
-        <v>2721</v>
+        <v>4592</v>
       </c>
       <c r="D3" t="n">
-        <v>13956</v>
+        <v>8310</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4596</v>
+        <v>630</v>
       </c>
       <c r="C4" t="n">
-        <v>3565</v>
+        <v>7381</v>
       </c>
       <c r="D4" t="n">
-        <v>12074</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3764</v>
+        <v>658</v>
       </c>
       <c r="C5" t="n">
-        <v>4982</v>
+        <v>8807</v>
       </c>
       <c r="D5" t="n">
-        <v>6224</v>
+        <v>5012</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1975</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>4991</v>
+        <v>8630</v>
       </c>
       <c r="D6" t="n">
-        <v>2127</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>488</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3375</v>
+        <v>5301</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1708</v>
+        <v>1834</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>622</v>
+        <v>498</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7336</v>
+        <v>389</v>
       </c>
       <c r="C2" t="n">
-        <v>3775</v>
+        <v>14354</v>
       </c>
       <c r="D2" t="n">
-        <v>12456</v>
+        <v>12550</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3611</v>
+        <v>263</v>
       </c>
       <c r="C3" t="n">
-        <v>2272</v>
+        <v>4925</v>
       </c>
       <c r="D3" t="n">
-        <v>12586</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3907</v>
+        <v>428</v>
       </c>
       <c r="C4" t="n">
-        <v>3110</v>
+        <v>5915</v>
       </c>
       <c r="D4" t="n">
-        <v>11996</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3705</v>
+        <v>586</v>
       </c>
       <c r="C5" t="n">
-        <v>4266</v>
+        <v>7895</v>
       </c>
       <c r="D5" t="n">
-        <v>6877</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2441</v>
+        <v>432</v>
       </c>
       <c r="C6" t="n">
-        <v>4942</v>
+        <v>8625</v>
       </c>
       <c r="D6" t="n">
-        <v>2649</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>894</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>4022</v>
+        <v>6734</v>
       </c>
       <c r="D7" t="n">
-        <v>926</v>
+        <v>898</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>2361</v>
+        <v>3260</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9382</v>
+        <v>2135</v>
       </c>
       <c r="C2" t="n">
-        <v>5415</v>
+        <v>15125</v>
       </c>
       <c r="D2" t="n">
-        <v>6690</v>
+        <v>11779</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5081</v>
+        <v>839</v>
       </c>
       <c r="C2" t="n">
-        <v>2053</v>
+        <v>19566</v>
       </c>
       <c r="D2" t="n">
-        <v>9067</v>
+        <v>19062</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5063</v>
+        <v>258</v>
       </c>
       <c r="C3" t="n">
-        <v>2842</v>
+        <v>7700</v>
       </c>
       <c r="D3" t="n">
-        <v>13670</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5415</v>
+        <v>317</v>
       </c>
       <c r="C4" t="n">
-        <v>4478</v>
+        <v>5373</v>
       </c>
       <c r="D4" t="n">
-        <v>12409</v>
+        <v>7948</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2426</v>
+        <v>484</v>
       </c>
       <c r="C5" t="n">
-        <v>6636</v>
+        <v>6856</v>
       </c>
       <c r="D5" t="n">
-        <v>6289</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>5055</v>
+        <v>8263</v>
       </c>
       <c r="D6" t="n">
-        <v>2104</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>2313</v>
+        <v>7388</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>989</v>
+        <v>4552</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>1797</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>167</v>
+        <v>543</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7966</v>
+        <v>5221</v>
       </c>
       <c r="C2" t="n">
-        <v>2983</v>
+        <v>9238</v>
       </c>
       <c r="D2" t="n">
-        <v>13082</v>
+        <v>25975</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3983</v>
+        <v>708</v>
       </c>
       <c r="C3" t="n">
-        <v>2729</v>
+        <v>5972</v>
       </c>
       <c r="D3" t="n">
-        <v>1763</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5281</v>
+        <v>2546</v>
       </c>
       <c r="C2" t="n">
-        <v>5325</v>
+        <v>6464</v>
       </c>
       <c r="D2" t="n">
-        <v>16379</v>
+        <v>21394</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4912</v>
+        <v>2532</v>
       </c>
       <c r="C3" t="n">
-        <v>2477</v>
+        <v>6793</v>
       </c>
       <c r="D3" t="n">
-        <v>3534</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1764</v>
+        <v>355</v>
       </c>
       <c r="C4" t="n">
-        <v>1641</v>
+        <v>3718</v>
       </c>
       <c r="D4" t="n">
-        <v>1536</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5675</v>
+        <v>1669</v>
       </c>
       <c r="C2" t="n">
-        <v>3489</v>
+        <v>5031</v>
       </c>
       <c r="D2" t="n">
-        <v>24811</v>
+        <v>21564</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4204</v>
+        <v>2095</v>
       </c>
       <c r="C3" t="n">
-        <v>3488</v>
+        <v>5684</v>
       </c>
       <c r="D3" t="n">
-        <v>5334</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2832</v>
+        <v>1251</v>
       </c>
       <c r="C4" t="n">
-        <v>2080</v>
+        <v>5470</v>
       </c>
       <c r="D4" t="n">
-        <v>1872</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>990</v>
+        <v>2225</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8729</v>
+        <v>1506</v>
       </c>
       <c r="C2" t="n">
-        <v>3838</v>
+        <v>8076</v>
       </c>
       <c r="D2" t="n">
-        <v>24489</v>
+        <v>19596</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4032</v>
+        <v>1564</v>
       </c>
       <c r="C3" t="n">
-        <v>3036</v>
+        <v>4611</v>
       </c>
       <c r="D3" t="n">
-        <v>7918</v>
+        <v>9842</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2986</v>
+        <v>1439</v>
       </c>
       <c r="C4" t="n">
-        <v>2773</v>
+        <v>5477</v>
       </c>
       <c r="D4" t="n">
-        <v>2428</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1515</v>
+        <v>600</v>
       </c>
       <c r="C5" t="n">
-        <v>1544</v>
+        <v>3954</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>395</v>
+        <v>142</v>
       </c>
       <c r="C6" t="n">
-        <v>649</v>
+        <v>1295</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9184</v>
+        <v>1744</v>
       </c>
       <c r="C2" t="n">
-        <v>4256</v>
+        <v>14228</v>
       </c>
       <c r="D2" t="n">
-        <v>30764</v>
+        <v>19075</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4609</v>
+        <v>1273</v>
       </c>
       <c r="C3" t="n">
-        <v>2827</v>
+        <v>5545</v>
       </c>
       <c r="D3" t="n">
-        <v>9294</v>
+        <v>10631</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2193</v>
+        <v>1299</v>
       </c>
       <c r="C4" t="n">
-        <v>2395</v>
+        <v>4905</v>
       </c>
       <c r="D4" t="n">
-        <v>2908</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1182</v>
+        <v>855</v>
       </c>
       <c r="C5" t="n">
-        <v>1603</v>
+        <v>4608</v>
       </c>
       <c r="D5" t="n">
-        <v>1180</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>737</v>
+        <v>2608</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>784</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7209</v>
+        <v>3704</v>
       </c>
       <c r="C2" t="n">
-        <v>4066</v>
+        <v>18819</v>
       </c>
       <c r="D2" t="n">
-        <v>21591</v>
+        <v>22684</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5773</v>
+        <v>1218</v>
       </c>
       <c r="C3" t="n">
-        <v>3156</v>
+        <v>8473</v>
       </c>
       <c r="D3" t="n">
-        <v>12373</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3017</v>
+        <v>1108</v>
       </c>
       <c r="C4" t="n">
-        <v>2610</v>
+        <v>5122</v>
       </c>
       <c r="D4" t="n">
-        <v>4168</v>
+        <v>5468</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1517</v>
+        <v>938</v>
       </c>
       <c r="C5" t="n">
-        <v>2025</v>
+        <v>4654</v>
       </c>
       <c r="D5" t="n">
-        <v>1492</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>760</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>1234</v>
+        <v>3477</v>
       </c>
       <c r="D6" t="n">
-        <v>820</v>
+        <v>998</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>560</v>
+        <v>1623</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>513</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8328</v>
+        <v>3170</v>
       </c>
       <c r="C2" t="n">
-        <v>9403</v>
+        <v>11893</v>
       </c>
       <c r="D2" t="n">
-        <v>28434</v>
+        <v>17997</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5342</v>
+        <v>1774</v>
       </c>
       <c r="C3" t="n">
-        <v>3163</v>
+        <v>13065</v>
       </c>
       <c r="D3" t="n">
-        <v>12957</v>
+        <v>12394</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3770</v>
+        <v>866</v>
       </c>
       <c r="C4" t="n">
-        <v>2845</v>
+        <v>7614</v>
       </c>
       <c r="D4" t="n">
-        <v>5576</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2002</v>
+        <v>455</v>
       </c>
       <c r="C5" t="n">
-        <v>2314</v>
+        <v>3407</v>
       </c>
       <c r="D5" t="n">
-        <v>1960</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>165</v>
       </c>
       <c r="C6" t="n">
-        <v>1652</v>
+        <v>1590</v>
       </c>
       <c r="D6" t="n">
-        <v>923</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>923</v>
+        <v>502</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>423</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
